--- a/data/Table2_all.xlsx
+++ b/data/Table2_all.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dtudk-my.sharepoint.com/personal/aeja_dtu_dk/Documents/Dokumenter/GitHub/Dietary_Risk_Factor_Database/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{BC8B6BFB-2492-4C9D-938A-321B5CD059F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18F0DE55-845E-40F1-8540-B3058048E91B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{BC8B6BFB-2492-4C9D-938A-321B5CD059F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40100D7E-CF6F-43D5-882F-FB2382230473}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{ABDB564E-6E13-467C-8C31-230DD443BDF3}"/>
   </bookViews>
@@ -810,9 +810,6 @@
     <t>19,044 (1,090)</t>
   </si>
   <si>
-    <t>0.97 [0.82, 1.14]</t>
-  </si>
-  <si>
     <t>30g/day</t>
   </si>
   <si>
@@ -861,9 +858,6 @@
     <t>20,325 (1,133)</t>
   </si>
   <si>
-    <t>1.50 [1.16, 1.94]</t>
-  </si>
-  <si>
     <t>Processed Meat</t>
   </si>
   <si>
@@ -948,9 +942,6 @@
     <t>33% (0.223)</t>
   </si>
   <si>
-    <t>1.34 [0.96 – 0.86]</t>
-  </si>
-  <si>
     <t>0% (0.45)</t>
   </si>
   <si>
@@ -1041,9 +1032,6 @@
     <t>2,413,032 (16,202)</t>
   </si>
   <si>
-    <t>1.30 [1.01- 1.64]</t>
-  </si>
-  <si>
     <r>
       <t>Two Star</t>
     </r>
@@ -1530,9 +1518,6 @@
     <t>818,059 (-)</t>
   </si>
   <si>
-    <t>0.91 [-] </t>
-  </si>
-  <si>
     <t>Oesophageal Cancer</t>
   </si>
   <si>
@@ -1542,9 +1527,6 @@
     <t>1,952,226 (41,494)</t>
   </si>
   <si>
-    <t>0.81 [-]</t>
-  </si>
-  <si>
     <r>
       <t>Three Star</t>
     </r>
@@ -1563,18 +1545,12 @@
     <t>829,610 (-)</t>
   </si>
   <si>
-    <t>0.80 [-]</t>
-  </si>
-  <si>
     <t>Ischemic Stroke</t>
   </si>
   <si>
     <t>646,338 (-)</t>
   </si>
   <si>
-    <t>0.84 [-]</t>
-  </si>
-  <si>
     <t>Hemorrhagic Stroke</t>
   </si>
   <si>
@@ -2371,9 +2347,6 @@
   </si>
   <si>
     <t>2,500,000 (person-years)</t>
-  </si>
-  <si>
-    <t>0.81 [0.73, 0.90]</t>
   </si>
   <si>
     <t>79% (&lt;0.001)</t>
@@ -2882,6 +2855,33 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>1.30 [1.01-1.64]</t>
+  </si>
+  <si>
+    <t>1.50 [1.16-1.94]</t>
+  </si>
+  <si>
+    <t>0.97 [0.82-1.14]</t>
+  </si>
+  <si>
+    <t>0.84 [0.72-0.98]</t>
+  </si>
+  <si>
+    <t>0.80 [0.75-0.84]</t>
+  </si>
+  <si>
+    <t>0.81 [0.74-0.88]</t>
+  </si>
+  <si>
+    <t>0.91 [0.84-0.99] </t>
+  </si>
+  <si>
+    <t>0.81 [0.73-0.90]</t>
+  </si>
+  <si>
+    <t>1.34 [0.96-1.86]</t>
   </si>
 </sst>
 </file>
@@ -3451,45 +3451,45 @@
   <sheetData>
     <row r="1" spans="1:12" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="G1" s="22" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="K1" s="22" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="B2" s="9"/>
       <c r="C2" s="9"/>
@@ -3505,25 +3505,25 @@
     </row>
     <row r="3" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="F3" s="3">
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3532,10 +3532,10 @@
         <v>70</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>0</v>
@@ -3543,16 +3543,16 @@
     </row>
     <row r="4" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>153</v>
@@ -3561,16 +3561,16 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>121</v>
@@ -3581,31 +3581,31 @@
     </row>
     <row r="5" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="F5" s="2">
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>11</v>
@@ -3619,19 +3619,19 @@
     </row>
     <row r="6" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -3643,7 +3643,7 @@
         <v>21</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>77</v>
@@ -3657,19 +3657,19 @@
     </row>
     <row r="7" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="F7" s="2">
         <v>7</v>
@@ -3682,13 +3682,13 @@
         <v>21</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>17</v>
@@ -3696,16 +3696,16 @@
     </row>
     <row r="8" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>92</v>
@@ -3721,13 +3721,13 @@
         <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>17</v>
@@ -3735,19 +3735,19 @@
     </row>
     <row r="9" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
@@ -3760,13 +3760,13 @@
         <v>21</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>17</v>
@@ -3774,19 +3774,19 @@
     </row>
     <row r="10" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="F10" s="2">
         <v>3</v>
@@ -3799,13 +3799,13 @@
         <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>54</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>17</v>
@@ -3816,31 +3816,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="F11" s="2">
         <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>121</v>
@@ -3854,13 +3854,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>43</v>
@@ -3869,16 +3869,16 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>121</v>
@@ -3889,19 +3889,19 @@
     </row>
     <row r="13" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="F13" s="2">
         <v>5</v>
@@ -3913,7 +3913,7 @@
         <v>21</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>77</v>
@@ -3927,19 +3927,19 @@
     </row>
     <row r="14" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="F14" s="2">
         <v>7</v>
@@ -3951,7 +3951,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>77</v>
@@ -3965,19 +3965,19 @@
     </row>
     <row r="15" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="F15" s="2">
         <v>5</v>
@@ -3987,16 +3987,16 @@
         <v>-1.1619999999999999</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>17</v>
@@ -4004,19 +4004,19 @@
     </row>
     <row r="16" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>489</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="F16" s="2">
         <v>8</v>
@@ -4028,7 +4028,7 @@
         <v>21</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>94</v>
@@ -4042,19 +4042,19 @@
     </row>
     <row r="17" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F17" s="2">
         <v>7</v>
@@ -4066,7 +4066,7 @@
         <v>21</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>94</v>
@@ -4080,19 +4080,19 @@
     </row>
     <row r="18" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F18" s="2">
         <v>3</v>
@@ -4104,7 +4104,7 @@
         <v>21</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>77</v>
@@ -4118,19 +4118,19 @@
     </row>
     <row r="19" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="F19" s="2">
         <v>7</v>
@@ -4142,7 +4142,7 @@
         <v>21</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>77</v>
@@ -4156,19 +4156,19 @@
     </row>
     <row r="20" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F20" s="2">
         <v>5</v>
@@ -4180,7 +4180,7 @@
         <v>21</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>77</v>
@@ -4197,16 +4197,16 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="F21" s="2">
         <v>6</v>
@@ -4218,7 +4218,7 @@
         <v>13</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>94</v>
@@ -4235,16 +4235,16 @@
         <v>10</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F22" s="2">
         <v>6</v>
@@ -4256,7 +4256,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>11</v>
@@ -4270,19 +4270,19 @@
     </row>
     <row r="23" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F23" s="2">
         <v>5</v>
@@ -4294,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>77</v>
@@ -4308,19 +4308,19 @@
     </row>
     <row r="24" spans="1:12" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="F24" s="9">
         <v>2</v>
@@ -4332,7 +4332,7 @@
         <v>21</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>77</v>
@@ -4346,7 +4346,7 @@
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4362,37 +4362,37 @@
     </row>
     <row r="26" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F26" s="2">
         <v>9</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>17</v>
@@ -4400,37 +4400,37 @@
     </row>
     <row r="27" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2">
         <v>7</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>17</v>
@@ -4438,37 +4438,37 @@
     </row>
     <row r="28" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F28" s="2">
         <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>17</v>
@@ -4476,37 +4476,37 @@
     </row>
     <row r="29" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F29" s="2">
         <v>3</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>17</v>
@@ -4514,37 +4514,37 @@
     </row>
     <row r="30" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="F30" s="2">
         <v>5</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>17</v>
@@ -4552,37 +4552,37 @@
     </row>
     <row r="31" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F31" s="2">
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>17</v>
@@ -4590,37 +4590,37 @@
     </row>
     <row r="32" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="F32" s="2">
         <v>3</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>17</v>
@@ -4628,37 +4628,37 @@
     </row>
     <row r="33" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F33" s="2">
         <v>3</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>17</v>
@@ -4666,37 +4666,37 @@
     </row>
     <row r="34" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F34" s="2">
         <v>7</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>77</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L34" s="17" t="s">
         <v>17</v>
@@ -4704,37 +4704,37 @@
     </row>
     <row r="35" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F35" s="2">
         <v>17</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L35" s="17" t="s">
         <v>17</v>
@@ -4742,37 +4742,37 @@
     </row>
     <row r="36" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="F36" s="2">
         <v>20</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L36" s="17" t="s">
         <v>17</v>
@@ -4780,37 +4780,37 @@
     </row>
     <row r="37" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>98</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="F37" s="2">
         <v>8</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L37" s="17" t="s">
         <v>17</v>
@@ -4818,37 +4818,37 @@
     </row>
     <row r="38" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>88</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>434</v>
+        <v>552</v>
       </c>
       <c r="F38" s="2">
         <v>9</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L38" s="17" t="s">
         <v>17</v>
@@ -4856,37 +4856,37 @@
     </row>
     <row r="39" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>431</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F39" s="2">
         <v>9</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>17</v>
@@ -4894,37 +4894,37 @@
     </row>
     <row r="40" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>82</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="F40" s="2">
         <v>11</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>17</v>
@@ -4932,37 +4932,37 @@
     </row>
     <row r="41" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="F41" s="2">
         <v>11</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>94</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>17</v>
@@ -4970,10 +4970,10 @@
     </row>
     <row r="42" spans="1:12" ht="55.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>110</v>
@@ -4982,19 +4982,19 @@
         <v>81</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="F42" s="2">
         <v>14</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>94</v>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="43" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>102</v>
@@ -5020,19 +5020,19 @@
         <v>81</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="F43" s="2">
         <v>7</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>94</v>
@@ -5046,10 +5046,10 @@
     </row>
     <row r="44" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>93</v>
@@ -5058,19 +5058,19 @@
         <v>81</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="F44" s="2">
         <v>13</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>94</v>
@@ -5084,31 +5084,31 @@
     </row>
     <row r="45" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F45" s="2">
         <v>7</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>77</v>
@@ -5122,31 +5122,31 @@
     </row>
     <row r="46" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="F46" s="2">
         <v>7</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>77</v>
@@ -5160,31 +5160,31 @@
     </row>
     <row r="47" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F47" s="2">
         <v>5</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>77</v>
@@ -5198,31 +5198,31 @@
     </row>
     <row r="48" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F48" s="2">
         <v>5</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>77</v>
@@ -5236,31 +5236,31 @@
     </row>
     <row r="49" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="F49" s="2">
         <v>5</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>77</v>
@@ -5274,31 +5274,31 @@
     </row>
     <row r="50" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>102</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="F50" s="2">
         <v>2</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>94</v>
@@ -5312,31 +5312,31 @@
     </row>
     <row r="51" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="F51" s="2">
         <v>5</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>94</v>
@@ -5350,31 +5350,31 @@
     </row>
     <row r="52" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="F52" s="2">
         <v>4</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>77</v>
@@ -5388,31 +5388,31 @@
     </row>
     <row r="53" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="F53" s="2">
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>94</v>
@@ -5426,31 +5426,31 @@
     </row>
     <row r="54" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="F54" s="2">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>77</v>
@@ -5464,31 +5464,31 @@
     </row>
     <row r="55" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>93</v>
       </c>
       <c r="D55" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="F55" s="2">
         <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>94</v>
@@ -5502,31 +5502,31 @@
     </row>
     <row r="56" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>110</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="F56" s="2">
         <v>4</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>94</v>
@@ -5540,31 +5540,31 @@
     </row>
     <row r="57" spans="1:12" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>93</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="F57" s="9">
         <v>4</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="H57" s="9" t="s">
         <v>21</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>94</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="58" spans="1:12" ht="68.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="10" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B58" s="9"/>
       <c r="C58" s="9"/>
@@ -5594,16 +5594,16 @@
     </row>
     <row r="59" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>62</v>
@@ -5619,7 +5619,7 @@
         <v>21</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>27</v>
@@ -5633,37 +5633,37 @@
     </row>
     <row r="60" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>355</v>
+        <v>548</v>
       </c>
       <c r="F60" s="2">
         <v>9</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I60" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>17</v>
@@ -5671,37 +5671,37 @@
     </row>
     <row r="61" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>352</v>
+        <v>549</v>
       </c>
       <c r="F61" s="2">
         <v>12</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I61" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>17</v>
@@ -5709,37 +5709,37 @@
     </row>
     <row r="62" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>349</v>
+        <v>550</v>
       </c>
       <c r="F62" s="2">
         <v>17</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I62" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>17</v>
@@ -5747,37 +5747,37 @@
     </row>
     <row r="63" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>345</v>
+        <v>551</v>
       </c>
       <c r="F63" s="2">
         <v>6</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I63" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>17</v>
@@ -5788,16 +5788,16 @@
         <v>10</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F64" s="2">
         <v>9</v>
@@ -5809,13 +5809,13 @@
         <v>13</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>0</v>
@@ -5826,22 +5826,22 @@
         <v>10</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F65" s="2">
         <v>8</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>13</v>
@@ -5850,7 +5850,7 @@
         <v>42</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>1</v>
@@ -5861,19 +5861,19 @@
     </row>
     <row r="66" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F66" s="2">
         <v>3</v>
@@ -5886,7 +5886,7 @@
         <v>21</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>54</v>
@@ -5900,19 +5900,19 @@
     </row>
     <row r="67" spans="1:12" ht="42" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F67" s="2">
         <v>11</v>
@@ -5931,7 +5931,7 @@
         <v>54</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>17</v>
@@ -5939,19 +5939,19 @@
     </row>
     <row r="68" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F68" s="2">
         <v>4</v>
@@ -5964,7 +5964,7 @@
         <v>21</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>54</v>
@@ -5978,19 +5978,19 @@
     </row>
     <row r="69" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="F69" s="2">
         <v>6</v>
@@ -6003,7 +6003,7 @@
         <v>21</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>54</v>
@@ -6017,19 +6017,19 @@
     </row>
     <row r="70" spans="1:12" ht="67.5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F70" s="2">
         <v>3</v>
@@ -6042,7 +6042,7 @@
         <v>21</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>54</v>
@@ -6056,19 +6056,19 @@
     </row>
     <row r="71" spans="1:12" ht="81" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F71" s="2">
         <v>4</v>
@@ -6081,13 +6081,13 @@
         <v>21</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>17</v>
@@ -6095,31 +6095,31 @@
     </row>
     <row r="72" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F72" s="2">
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>54</v>
@@ -6133,31 +6133,31 @@
     </row>
     <row r="73" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="F73" s="2">
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>27</v>
@@ -6171,19 +6171,19 @@
     </row>
     <row r="74" spans="1:12" ht="42" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F74" s="2">
         <v>13</v>
@@ -6202,7 +6202,7 @@
         <v>54</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>17</v>
@@ -6210,19 +6210,19 @@
     </row>
     <row r="75" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F75" s="2">
         <v>9</v>
@@ -6235,7 +6235,7 @@
         <v>21</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>54</v>
@@ -6249,19 +6249,19 @@
     </row>
     <row r="76" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F76" s="2">
         <v>5</v>
@@ -6274,7 +6274,7 @@
         <v>21</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>54</v>
@@ -6288,19 +6288,19 @@
     </row>
     <row r="77" spans="1:12" ht="81" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F77" s="2">
         <v>3</v>
@@ -6313,7 +6313,7 @@
         <v>21</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>54</v>
@@ -6327,19 +6327,19 @@
     </row>
     <row r="78" spans="1:12" ht="42" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F78" s="2">
         <v>13</v>
@@ -6352,13 +6352,13 @@
         <v>21</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>54</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>17</v>
@@ -6366,31 +6366,31 @@
     </row>
     <row r="79" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>132</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F79" s="2">
         <v>10</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>27</v>
@@ -6407,16 +6407,16 @@
         <v>10</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="F80" s="2">
         <v>7</v>
@@ -6428,13 +6428,13 @@
         <v>13</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>0</v>
@@ -6445,16 +6445,16 @@
         <v>10</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F81" s="2">
         <v>4</v>
@@ -6466,10 +6466,10 @@
         <v>4</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>1</v>
@@ -6480,19 +6480,19 @@
     </row>
     <row r="82" spans="1:12" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F82" s="2">
         <v>3</v>
@@ -6505,7 +6505,7 @@
         <v>21</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>54</v>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="83" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -6535,19 +6535,19 @@
     </row>
     <row r="84" spans="1:12" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F84" s="9">
         <v>2</v>
@@ -6559,7 +6559,7 @@
         <v>21</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="J84" s="9" t="s">
         <v>77</v>
@@ -6573,7 +6573,7 @@
     </row>
     <row r="85" spans="1:12" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="10" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
@@ -6592,16 +6592,16 @@
         <v>10</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F86" s="2">
         <v>2</v>
@@ -6613,7 +6613,7 @@
         <v>13</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>11</v>
@@ -6630,28 +6630,28 @@
         <v>10</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F87" s="2">
         <v>2</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>11</v>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="88" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -6681,31 +6681,31 @@
     </row>
     <row r="89" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>27</v>
@@ -6719,31 +6719,31 @@
     </row>
     <row r="90" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="F90" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>27</v>
@@ -6757,22 +6757,22 @@
     </row>
     <row r="91" spans="1:12" ht="41.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>14</v>
@@ -6781,7 +6781,7 @@
         <v>21</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J91" s="9" t="s">
         <v>27</v>
@@ -6795,7 +6795,7 @@
     </row>
     <row r="92" spans="1:12" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="10" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
@@ -6814,16 +6814,16 @@
         <v>157</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F93" s="2">
         <v>18</v>
@@ -6836,7 +6836,7 @@
         <v>21</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>54</v>
@@ -6853,16 +6853,16 @@
         <v>157</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F94" s="2">
         <v>4</v>
@@ -6892,16 +6892,16 @@
         <v>126</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F95" s="2">
         <v>2</v>
@@ -6930,16 +6930,16 @@
         <v>126</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F96" s="2">
         <v>3</v>
@@ -6951,7 +6951,7 @@
         <v>21</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>94</v>
@@ -6968,16 +6968,16 @@
         <v>126</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>149</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F97" s="2">
         <v>5</v>
@@ -6989,10 +6989,10 @@
         <v>21</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="K97" s="3" t="s">
         <v>1</v>
@@ -7006,16 +7006,16 @@
         <v>126</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F98" s="2">
         <v>3</v>
@@ -7027,7 +7027,7 @@
         <v>21</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>77</v>
@@ -7044,16 +7044,16 @@
         <v>117</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F99" s="2">
         <v>5</v>
@@ -7065,7 +7065,7 @@
         <v>21</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>77</v>
@@ -7082,28 +7082,28 @@
         <v>10</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F100" s="2">
         <v>4</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>11</v>
@@ -7120,28 +7120,28 @@
         <v>10</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F101" s="2">
         <v>4</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>11</v>
@@ -7155,7 +7155,7 @@
     </row>
     <row r="102" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -7171,34 +7171,34 @@
     </row>
     <row r="103" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F103" s="2">
         <v>10</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I103" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>51</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="104" spans="1:12" ht="81" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>69</v>
@@ -7221,22 +7221,22 @@
         <v>114</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>226</v>
+        <v>545</v>
       </c>
       <c r="F104" s="2">
         <v>21</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I104" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J104" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>51</v>
@@ -7247,34 +7247,34 @@
     </row>
     <row r="105" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F105" s="2">
         <v>11</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I105" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J105" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>51</v>
@@ -7285,34 +7285,34 @@
     </row>
     <row r="106" spans="1:12" ht="40.5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F106" s="2">
         <v>17</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I106" s="15" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>51</v>
@@ -7326,16 +7326,16 @@
         <v>10</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F107" s="2">
         <v>5</v>
@@ -7347,7 +7347,7 @@
         <v>13</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>11</v>
@@ -7364,16 +7364,16 @@
         <v>10</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F108" s="2">
         <v>3</v>
@@ -7385,10 +7385,10 @@
         <v>13</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K108" s="3" t="s">
         <v>1</v>
@@ -7402,16 +7402,16 @@
         <v>157</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F109" s="2">
         <v>7</v>
@@ -7441,16 +7441,16 @@
         <v>157</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>44</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F110" s="2">
         <v>8</v>
@@ -7463,13 +7463,13 @@
         <v>21</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>54</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>17</v>
@@ -7480,16 +7480,16 @@
         <v>126</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F111" s="2">
         <v>3</v>
@@ -7501,7 +7501,7 @@
         <v>21</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>77</v>
@@ -7518,16 +7518,16 @@
         <v>117</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>203</v>
+        <v>553</v>
       </c>
       <c r="F112" s="2">
         <v>3</v>
@@ -7539,7 +7539,7 @@
         <v>21</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>77</v>
@@ -7553,31 +7553,31 @@
     </row>
     <row r="113" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F113" s="2">
         <v>4</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>94</v>
@@ -7594,7 +7594,7 @@
         <v>10</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>16</v>
@@ -7603,7 +7603,7 @@
         <v>114</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F114" s="2">
         <v>7</v>
@@ -7615,7 +7615,7 @@
         <v>13</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>11</v>
@@ -7632,28 +7632,28 @@
         <v>10</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F115" s="2">
         <v>3</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>13</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>11</v>
@@ -7670,7 +7670,7 @@
         <v>157</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>69</v>
@@ -7679,7 +7679,7 @@
         <v>114</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F116" s="2">
         <v>10</v>
@@ -7692,7 +7692,7 @@
         <v>21</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>19</v>
@@ -7709,7 +7709,7 @@
         <v>157</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>57</v>
@@ -7718,7 +7718,7 @@
         <v>114</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F117" s="2">
         <v>7</v>
@@ -7748,16 +7748,16 @@
         <v>157</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F118" s="2">
         <v>2</v>
@@ -7787,7 +7787,7 @@
         <v>157</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>44</v>
@@ -7796,7 +7796,7 @@
         <v>114</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F119" s="2">
         <v>7</v>
@@ -7826,16 +7826,16 @@
         <v>157</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>114</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F120" s="2">
         <v>3</v>
@@ -7848,7 +7848,7 @@
         <v>21</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>54</v>
@@ -7862,31 +7862,31 @@
     </row>
     <row r="121" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>182</v>
+        <v>546</v>
       </c>
       <c r="F121" s="2">
         <v>3</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>77</v>
@@ -7903,16 +7903,16 @@
         <v>126</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F122" s="2">
         <v>3</v>
@@ -7924,7 +7924,7 @@
         <v>21</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>77</v>
@@ -7941,28 +7941,28 @@
         <v>117</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>115</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F123" s="2">
         <v>3</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>77</v>
@@ -7976,25 +7976,25 @@
     </row>
     <row r="124" spans="1:12" ht="54" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F124" s="2">
         <v>2</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>21</v>
@@ -8017,16 +8017,16 @@
         <v>126</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>124</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F125" s="2">
         <v>2</v>
@@ -8052,19 +8052,19 @@
     </row>
     <row r="126" spans="1:12" ht="54.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>165</v>
+        <v>547</v>
       </c>
       <c r="F126" s="9">
         <v>3</v>
